--- a/firmware/custom/DU_Register_Definition_R4.xlsx
+++ b/firmware/custom/DU_Register_Definition_R4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPGA_Designs\IRT\L3H\SWCR\DU\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Dev\_CM_\Eglin\swc\swc-esw-src\firmware\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6E599D-E35C-46ED-A198-339A7DB26E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DF1003-1478-4353-8977-7D4D23497AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Memory Map" sheetId="2" r:id="rId1"/>
@@ -1229,16 +1229,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:E340"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="5.26171875" customWidth="1"/>
+    <col min="2" max="2" width="11.47265625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="71.26953125" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="71.26171875" customWidth="1"/>
+    <col min="5" max="5" width="12.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="10">
         <v>0</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="10">
         <f>B3+1</f>
         <v>1</v>
@@ -1283,7 +1283,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="10">
         <f t="shared" ref="B5:B34" si="1">B4+1</f>
         <v>2</v>
@@ -1299,7 +1299,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="10">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -1315,7 +1315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="10">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -1331,7 +1331,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="10">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="10">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -1363,7 +1363,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="10">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1379,7 +1379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="10">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1395,7 +1395,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="10">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1411,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="10">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1427,7 +1427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="10">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1443,7 +1443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="10">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1459,7 +1459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="10">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1475,7 +1475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="10">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1491,7 +1491,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="10">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -1507,7 +1507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="10">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -1523,7 +1523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="10">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -1539,7 +1539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="10">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1555,7 +1555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="10">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1571,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="10">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1587,7 +1587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="10">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1603,7 +1603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="10">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -1619,7 +1619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="10">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -1635,7 +1635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="10">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -1651,7 +1651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="10">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -1667,7 +1667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="10">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -1683,7 +1683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="10">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1699,7 +1699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="10">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1715,7 +1715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="10">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1731,7 +1731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="10">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -1747,7 +1747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="10">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -1763,7 +1763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="26" t="s">
         <v>37</v>
       </c>
@@ -1771,7 +1771,7 @@
       <c r="D35" s="27"/>
       <c r="E35" s="28"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="10">
         <f>1+B34</f>
         <v>32</v>
@@ -1788,7 +1788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="10">
         <f>1+B36</f>
         <v>33</v>
@@ -1805,7 +1805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="10">
         <f>1+B37</f>
         <v>34</v>
@@ -1822,7 +1822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="10">
         <f>1+B38</f>
         <v>35</v>
@@ -1839,7 +1839,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="10">
         <f t="shared" ref="B40:B103" si="4">1+B39</f>
         <v>36</v>
@@ -1856,7 +1856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="10">
         <f t="shared" si="4"/>
         <v>37</v>
@@ -1873,7 +1873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="10">
         <f t="shared" si="4"/>
         <v>38</v>
@@ -1890,7 +1890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="10">
         <f t="shared" si="4"/>
         <v>39</v>
@@ -1907,7 +1907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="10">
         <f t="shared" si="4"/>
         <v>40</v>
@@ -1924,7 +1924,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="10">
         <f t="shared" si="4"/>
         <v>41</v>
@@ -1941,7 +1941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="10">
         <f t="shared" si="4"/>
         <v>42</v>
@@ -1958,7 +1958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="10">
         <f t="shared" si="4"/>
         <v>43</v>
@@ -1975,7 +1975,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="10">
         <f t="shared" si="4"/>
         <v>44</v>
@@ -1992,7 +1992,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="10">
         <f t="shared" si="4"/>
         <v>45</v>
@@ -2009,7 +2009,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="10">
         <f t="shared" si="4"/>
         <v>46</v>
@@ -2026,7 +2026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="10">
         <f t="shared" si="4"/>
         <v>47</v>
@@ -2043,7 +2043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="10">
         <f t="shared" si="4"/>
         <v>48</v>
@@ -2060,7 +2060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="10">
         <f t="shared" si="4"/>
         <v>49</v>
@@ -2077,7 +2077,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="10">
         <f t="shared" si="4"/>
         <v>50</v>
@@ -2094,7 +2094,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="10">
         <f t="shared" si="4"/>
         <v>51</v>
@@ -2111,7 +2111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="10">
         <f t="shared" si="4"/>
         <v>52</v>
@@ -2128,7 +2128,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="10">
         <f t="shared" si="4"/>
         <v>53</v>
@@ -2145,7 +2145,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="10">
         <f t="shared" si="4"/>
         <v>54</v>
@@ -2162,7 +2162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="10">
         <f t="shared" si="4"/>
         <v>55</v>
@@ -2179,7 +2179,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="10">
         <f t="shared" si="4"/>
         <v>56</v>
@@ -2196,7 +2196,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="10">
         <f t="shared" si="4"/>
         <v>57</v>
@@ -2213,7 +2213,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="10">
         <f t="shared" si="4"/>
         <v>58</v>
@@ -2230,7 +2230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="10">
         <f t="shared" si="4"/>
         <v>59</v>
@@ -2247,7 +2247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="10">
         <f t="shared" si="4"/>
         <v>60</v>
@@ -2264,7 +2264,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="10">
         <f t="shared" si="4"/>
         <v>61</v>
@@ -2281,7 +2281,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="10">
         <f t="shared" si="4"/>
         <v>62</v>
@@ -2298,7 +2298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="10">
         <f t="shared" si="4"/>
         <v>63</v>
@@ -2315,7 +2315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="10">
         <f t="shared" si="4"/>
         <v>64</v>
@@ -2332,7 +2332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="10">
         <f t="shared" si="4"/>
         <v>65</v>
@@ -2349,7 +2349,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="10">
         <f t="shared" si="4"/>
         <v>66</v>
@@ -2366,7 +2366,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="10">
         <f t="shared" si="4"/>
         <v>67</v>
@@ -2383,7 +2383,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="10">
         <f t="shared" si="4"/>
         <v>68</v>
@@ -2400,7 +2400,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="10">
         <f t="shared" si="4"/>
         <v>69</v>
@@ -2417,7 +2417,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="10">
         <f t="shared" si="4"/>
         <v>70</v>
@@ -2434,7 +2434,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="10">
         <f t="shared" si="4"/>
         <v>71</v>
@@ -2451,7 +2451,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="10">
         <f t="shared" si="4"/>
         <v>72</v>
@@ -2468,7 +2468,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="10">
         <f t="shared" si="4"/>
         <v>73</v>
@@ -2485,7 +2485,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="10">
         <f t="shared" si="4"/>
         <v>74</v>
@@ -2502,7 +2502,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="10">
         <f t="shared" si="4"/>
         <v>75</v>
@@ -2519,7 +2519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="10">
         <f t="shared" si="4"/>
         <v>76</v>
@@ -2536,7 +2536,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="10">
         <f t="shared" si="4"/>
         <v>77</v>
@@ -2553,7 +2553,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="10">
         <f t="shared" si="4"/>
         <v>78</v>
@@ -2570,7 +2570,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="10">
         <f t="shared" si="4"/>
         <v>79</v>
@@ -2587,7 +2587,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="10">
         <f t="shared" si="4"/>
         <v>80</v>
@@ -2604,7 +2604,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="10">
         <f t="shared" si="4"/>
         <v>81</v>
@@ -2621,7 +2621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="10">
         <f t="shared" si="4"/>
         <v>82</v>
@@ -2638,7 +2638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="10">
         <f t="shared" si="4"/>
         <v>83</v>
@@ -2655,7 +2655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="10">
         <f t="shared" si="4"/>
         <v>84</v>
@@ -2672,7 +2672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="10">
         <f t="shared" si="4"/>
         <v>85</v>
@@ -2689,7 +2689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="10">
         <f t="shared" si="4"/>
         <v>86</v>
@@ -2706,7 +2706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="10">
         <f t="shared" si="4"/>
         <v>87</v>
@@ -2723,7 +2723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="10">
         <f t="shared" si="4"/>
         <v>88</v>
@@ -2740,7 +2740,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="10">
         <f t="shared" si="4"/>
         <v>89</v>
@@ -2757,7 +2757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="10">
         <f t="shared" si="4"/>
         <v>90</v>
@@ -2774,7 +2774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="10">
         <f t="shared" si="4"/>
         <v>91</v>
@@ -2791,7 +2791,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="10">
         <f t="shared" si="4"/>
         <v>92</v>
@@ -2808,7 +2808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="10">
         <f t="shared" si="4"/>
         <v>93</v>
@@ -2825,7 +2825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="10">
         <f t="shared" si="4"/>
         <v>94</v>
@@ -2842,7 +2842,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="10">
         <f t="shared" si="4"/>
         <v>95</v>
@@ -2859,7 +2859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="10">
         <f t="shared" si="4"/>
         <v>96</v>
@@ -2876,7 +2876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="10">
         <f t="shared" si="4"/>
         <v>97</v>
@@ -2893,7 +2893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="10">
         <f t="shared" si="4"/>
         <v>98</v>
@@ -2910,7 +2910,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="10">
         <f t="shared" si="4"/>
         <v>99</v>
@@ -2927,7 +2927,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="10">
         <f t="shared" ref="B104:B167" si="7">1+B103</f>
         <v>100</v>
@@ -2944,7 +2944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="10">
         <f t="shared" si="7"/>
         <v>101</v>
@@ -2961,7 +2961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="10">
         <f t="shared" si="7"/>
         <v>102</v>
@@ -2978,7 +2978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="10">
         <f t="shared" si="7"/>
         <v>103</v>
@@ -2995,7 +2995,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" s="10">
         <f t="shared" si="7"/>
         <v>104</v>
@@ -3012,7 +3012,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="10">
         <f t="shared" si="7"/>
         <v>105</v>
@@ -3029,7 +3029,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="10">
         <f t="shared" si="7"/>
         <v>106</v>
@@ -3046,7 +3046,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" s="10">
         <f t="shared" si="7"/>
         <v>107</v>
@@ -3063,7 +3063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" s="10">
         <f t="shared" si="7"/>
         <v>108</v>
@@ -3080,7 +3080,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" s="10">
         <f t="shared" si="7"/>
         <v>109</v>
@@ -3097,7 +3097,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="10">
         <f t="shared" si="7"/>
         <v>110</v>
@@ -3114,7 +3114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="10">
         <f t="shared" si="7"/>
         <v>111</v>
@@ -3131,7 +3131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" s="10">
         <f t="shared" si="7"/>
         <v>112</v>
@@ -3148,7 +3148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" s="10">
         <f t="shared" si="7"/>
         <v>113</v>
@@ -3165,7 +3165,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" s="10">
         <f t="shared" si="7"/>
         <v>114</v>
@@ -3182,7 +3182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" s="10">
         <f t="shared" si="7"/>
         <v>115</v>
@@ -3199,7 +3199,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" s="10">
         <f t="shared" si="7"/>
         <v>116</v>
@@ -3216,7 +3216,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" s="10">
         <f t="shared" si="7"/>
         <v>117</v>
@@ -3233,7 +3233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" s="10">
         <f t="shared" si="7"/>
         <v>118</v>
@@ -3250,7 +3250,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" s="10">
         <f t="shared" si="7"/>
         <v>119</v>
@@ -3267,7 +3267,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" s="10">
         <f t="shared" si="7"/>
         <v>120</v>
@@ -3284,7 +3284,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" s="10">
         <f t="shared" si="7"/>
         <v>121</v>
@@ -3301,7 +3301,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" s="10">
         <f t="shared" si="7"/>
         <v>122</v>
@@ -3318,7 +3318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B127" s="10">
         <f t="shared" si="7"/>
         <v>123</v>
@@ -3335,7 +3335,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B128" s="10">
         <f t="shared" si="7"/>
         <v>124</v>
@@ -3352,7 +3352,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" s="10">
         <f t="shared" si="7"/>
         <v>125</v>
@@ -3369,7 +3369,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" s="10">
         <f t="shared" si="7"/>
         <v>126</v>
@@ -3386,7 +3386,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" s="10">
         <f t="shared" si="7"/>
         <v>127</v>
@@ -3403,7 +3403,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B132" s="10">
         <f t="shared" si="7"/>
         <v>128</v>
@@ -3420,7 +3420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" s="10">
         <f t="shared" si="7"/>
         <v>129</v>
@@ -3437,7 +3437,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B134" s="10">
         <f t="shared" si="7"/>
         <v>130</v>
@@ -3454,7 +3454,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B135" s="10">
         <f t="shared" si="7"/>
         <v>131</v>
@@ -3471,7 +3471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B136" s="10">
         <f t="shared" si="7"/>
         <v>132</v>
@@ -3488,7 +3488,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B137" s="10">
         <f t="shared" si="7"/>
         <v>133</v>
@@ -3505,7 +3505,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B138" s="10">
         <f t="shared" si="7"/>
         <v>134</v>
@@ -3522,7 +3522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B139" s="10">
         <f t="shared" si="7"/>
         <v>135</v>
@@ -3539,7 +3539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B140" s="10">
         <f t="shared" si="7"/>
         <v>136</v>
@@ -3556,7 +3556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B141" s="10">
         <f t="shared" si="7"/>
         <v>137</v>
@@ -3573,7 +3573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B142" s="10">
         <f t="shared" si="7"/>
         <v>138</v>
@@ -3590,7 +3590,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B143" s="10">
         <f t="shared" si="7"/>
         <v>139</v>
@@ -3607,7 +3607,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B144" s="10">
         <f t="shared" si="7"/>
         <v>140</v>
@@ -3624,7 +3624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="10">
         <f t="shared" si="7"/>
         <v>141</v>
@@ -3641,7 +3641,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B146" s="10">
         <f t="shared" si="7"/>
         <v>142</v>
@@ -3658,7 +3658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B147" s="10">
         <f t="shared" si="7"/>
         <v>143</v>
@@ -3675,7 +3675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B148" s="10">
         <f t="shared" si="7"/>
         <v>144</v>
@@ -3692,7 +3692,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B149" s="10">
         <f t="shared" si="7"/>
         <v>145</v>
@@ -3709,7 +3709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B150" s="10">
         <f t="shared" si="7"/>
         <v>146</v>
@@ -3726,7 +3726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" s="10">
         <f t="shared" si="7"/>
         <v>147</v>
@@ -3743,7 +3743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B152" s="10">
         <f t="shared" si="7"/>
         <v>148</v>
@@ -3760,7 +3760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B153" s="10">
         <f t="shared" si="7"/>
         <v>149</v>
@@ -3777,7 +3777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B154" s="10">
         <f t="shared" si="7"/>
         <v>150</v>
@@ -3794,7 +3794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B155" s="10">
         <f t="shared" si="7"/>
         <v>151</v>
@@ -3811,7 +3811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B156" s="10">
         <f t="shared" si="7"/>
         <v>152</v>
@@ -3828,7 +3828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B157" s="10">
         <f t="shared" si="7"/>
         <v>153</v>
@@ -3845,7 +3845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B158" s="10">
         <f t="shared" si="7"/>
         <v>154</v>
@@ -3862,7 +3862,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B159" s="10">
         <f t="shared" si="7"/>
         <v>155</v>
@@ -3879,7 +3879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B160" s="10">
         <f t="shared" si="7"/>
         <v>156</v>
@@ -3896,7 +3896,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B161" s="10">
         <f t="shared" si="7"/>
         <v>157</v>
@@ -3913,7 +3913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B162" s="10">
         <f t="shared" si="7"/>
         <v>158</v>
@@ -3930,7 +3930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B163" s="10">
         <f t="shared" si="7"/>
         <v>159</v>
@@ -3947,7 +3947,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" s="10">
         <f t="shared" si="7"/>
         <v>160</v>
@@ -3964,7 +3964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B165" s="10">
         <f t="shared" si="7"/>
         <v>161</v>
@@ -3981,7 +3981,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B166" s="10">
         <f t="shared" si="7"/>
         <v>162</v>
@@ -3998,7 +3998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B167" s="10">
         <f t="shared" si="7"/>
         <v>163</v>
@@ -4015,7 +4015,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B168" s="10">
         <f t="shared" ref="B168:B187" si="10">1+B167</f>
         <v>164</v>
@@ -4032,7 +4032,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" s="10">
         <f t="shared" si="10"/>
         <v>165</v>
@@ -4049,7 +4049,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B170" s="10">
         <f t="shared" si="10"/>
         <v>166</v>
@@ -4066,7 +4066,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B171" s="10">
         <f t="shared" si="10"/>
         <v>167</v>
@@ -4083,7 +4083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B172" s="10">
         <f t="shared" si="10"/>
         <v>168</v>
@@ -4100,7 +4100,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B173" s="10">
         <f t="shared" si="10"/>
         <v>169</v>
@@ -4117,7 +4117,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B174" s="10">
         <f t="shared" si="10"/>
         <v>170</v>
@@ -4134,7 +4134,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B175" s="10">
         <f t="shared" si="10"/>
         <v>171</v>
@@ -4151,7 +4151,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B176" s="10">
         <f t="shared" si="10"/>
         <v>172</v>
@@ -4168,7 +4168,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B177" s="10">
         <f t="shared" si="10"/>
         <v>173</v>
@@ -4185,7 +4185,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B178" s="10">
         <f t="shared" si="10"/>
         <v>174</v>
@@ -4202,7 +4202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B179" s="10">
         <f t="shared" si="10"/>
         <v>175</v>
@@ -4219,7 +4219,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B180" s="10">
         <f t="shared" si="10"/>
         <v>176</v>
@@ -4236,7 +4236,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B181" s="10">
         <f t="shared" si="10"/>
         <v>177</v>
@@ -4253,7 +4253,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B182" s="10">
         <f t="shared" si="10"/>
         <v>178</v>
@@ -4270,7 +4270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B183" s="10">
         <f t="shared" si="10"/>
         <v>179</v>
@@ -4287,7 +4287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" s="10">
         <f t="shared" si="10"/>
         <v>180</v>
@@ -4304,7 +4304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B185" s="10">
         <f t="shared" si="10"/>
         <v>181</v>
@@ -4321,7 +4321,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B186" s="10">
         <f t="shared" si="10"/>
         <v>182</v>
@@ -4338,7 +4338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B187" s="10">
         <f t="shared" si="10"/>
         <v>183</v>
@@ -4355,7 +4355,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B188" s="26" t="s">
         <v>77</v>
       </c>
@@ -4363,7 +4363,7 @@
       <c r="D188" s="27"/>
       <c r="E188" s="28"/>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B189" s="10">
         <f>1+B187</f>
         <v>184</v>
@@ -4380,7 +4380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B190" s="10">
         <f>1+B189</f>
         <v>185</v>
@@ -4397,7 +4397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B191" s="10">
         <f t="shared" ref="B191:B254" si="14">1+B190</f>
         <v>186</v>
@@ -4414,7 +4414,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B192" s="10">
         <f t="shared" si="14"/>
         <v>187</v>
@@ -4431,7 +4431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B193" s="10">
         <f t="shared" si="14"/>
         <v>188</v>
@@ -4448,7 +4448,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B194" s="10">
         <f t="shared" si="14"/>
         <v>189</v>
@@ -4465,7 +4465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B195" s="10">
         <f t="shared" si="14"/>
         <v>190</v>
@@ -4482,7 +4482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B196" s="10">
         <f t="shared" si="14"/>
         <v>191</v>
@@ -4499,7 +4499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B197" s="10">
         <f t="shared" si="14"/>
         <v>192</v>
@@ -4516,7 +4516,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B198" s="10">
         <f t="shared" si="14"/>
         <v>193</v>
@@ -4533,7 +4533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B199" s="10">
         <f t="shared" si="14"/>
         <v>194</v>
@@ -4550,7 +4550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B200" s="10">
         <f t="shared" si="14"/>
         <v>195</v>
@@ -4567,7 +4567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B201" s="10">
         <f t="shared" si="14"/>
         <v>196</v>
@@ -4584,7 +4584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B202" s="10">
         <f t="shared" si="14"/>
         <v>197</v>
@@ -4601,7 +4601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" s="10">
         <f t="shared" si="14"/>
         <v>198</v>
@@ -4618,7 +4618,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B204" s="10">
         <f t="shared" si="14"/>
         <v>199</v>
@@ -4635,7 +4635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B205" s="10">
         <f t="shared" si="14"/>
         <v>200</v>
@@ -4652,7 +4652,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B206" s="10">
         <f t="shared" si="14"/>
         <v>201</v>
@@ -4669,7 +4669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B207" s="10">
         <f t="shared" si="14"/>
         <v>202</v>
@@ -4686,7 +4686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B208" s="10">
         <f t="shared" si="14"/>
         <v>203</v>
@@ -4703,7 +4703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B209" s="10">
         <f t="shared" si="14"/>
         <v>204</v>
@@ -4720,7 +4720,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B210" s="10">
         <f t="shared" si="14"/>
         <v>205</v>
@@ -4737,7 +4737,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B211" s="10">
         <f t="shared" si="14"/>
         <v>206</v>
@@ -4754,7 +4754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B212" s="10">
         <f t="shared" si="14"/>
         <v>207</v>
@@ -4771,7 +4771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B213" s="10">
         <f t="shared" si="14"/>
         <v>208</v>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B214" s="10">
         <f t="shared" si="14"/>
         <v>209</v>
@@ -4805,7 +4805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B215" s="10">
         <f t="shared" si="14"/>
         <v>210</v>
@@ -4822,7 +4822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B216" s="10">
         <f t="shared" si="14"/>
         <v>211</v>
@@ -4839,7 +4839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B217" s="10">
         <f t="shared" si="14"/>
         <v>212</v>
@@ -4856,7 +4856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B218" s="10">
         <f t="shared" si="14"/>
         <v>213</v>
@@ -4873,7 +4873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B219" s="10">
         <f t="shared" si="14"/>
         <v>214</v>
@@ -4890,7 +4890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B220" s="10">
         <f t="shared" si="14"/>
         <v>215</v>
@@ -4907,7 +4907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B221" s="10">
         <f t="shared" si="14"/>
         <v>216</v>
@@ -4924,7 +4924,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B222" s="10">
         <f t="shared" si="14"/>
         <v>217</v>
@@ -4941,7 +4941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B223" s="10">
         <f t="shared" si="14"/>
         <v>218</v>
@@ -4958,7 +4958,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B224" s="10">
         <f t="shared" si="14"/>
         <v>219</v>
@@ -4975,7 +4975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B225" s="10">
         <f t="shared" si="14"/>
         <v>220</v>
@@ -4992,7 +4992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B226" s="10">
         <f t="shared" si="14"/>
         <v>221</v>
@@ -5009,7 +5009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B227" s="10">
         <f t="shared" si="14"/>
         <v>222</v>
@@ -5026,7 +5026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B228" s="10">
         <f t="shared" si="14"/>
         <v>223</v>
@@ -5043,7 +5043,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B229" s="10">
         <f t="shared" si="14"/>
         <v>224</v>
@@ -5060,7 +5060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B230" s="10">
         <f t="shared" si="14"/>
         <v>225</v>
@@ -5077,7 +5077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B231" s="10">
         <f t="shared" si="14"/>
         <v>226</v>
@@ -5094,7 +5094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B232" s="10">
         <f t="shared" si="14"/>
         <v>227</v>
@@ -5111,7 +5111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B233" s="10">
         <f t="shared" si="14"/>
         <v>228</v>
@@ -5128,7 +5128,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B234" s="10">
         <f t="shared" si="14"/>
         <v>229</v>
@@ -5145,7 +5145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B235" s="10">
         <f t="shared" si="14"/>
         <v>230</v>
@@ -5162,7 +5162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B236" s="10">
         <f t="shared" si="14"/>
         <v>231</v>
@@ -5179,7 +5179,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B237" s="10">
         <f t="shared" si="14"/>
         <v>232</v>
@@ -5196,7 +5196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B238" s="10">
         <f t="shared" si="14"/>
         <v>233</v>
@@ -5213,7 +5213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B239" s="10">
         <f t="shared" si="14"/>
         <v>234</v>
@@ -5230,7 +5230,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B240" s="10">
         <f t="shared" si="14"/>
         <v>235</v>
@@ -5247,7 +5247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B241" s="10">
         <f t="shared" si="14"/>
         <v>236</v>
@@ -5264,7 +5264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B242" s="10">
         <f t="shared" si="14"/>
         <v>237</v>
@@ -5281,7 +5281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B243" s="10">
         <f t="shared" si="14"/>
         <v>238</v>
@@ -5298,7 +5298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B244" s="10">
         <f t="shared" si="14"/>
         <v>239</v>
@@ -5315,7 +5315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B245" s="10">
         <f t="shared" si="14"/>
         <v>240</v>
@@ -5332,7 +5332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B246" s="10">
         <f t="shared" si="14"/>
         <v>241</v>
@@ -5349,7 +5349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B247" s="10">
         <f t="shared" si="14"/>
         <v>242</v>
@@ -5366,7 +5366,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B248" s="10">
         <f t="shared" si="14"/>
         <v>243</v>
@@ -5383,7 +5383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B249" s="10">
         <f t="shared" si="14"/>
         <v>244</v>
@@ -5400,7 +5400,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B250" s="10">
         <f t="shared" si="14"/>
         <v>245</v>
@@ -5417,7 +5417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B251" s="10">
         <f t="shared" si="14"/>
         <v>246</v>
@@ -5434,7 +5434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B252" s="10">
         <f t="shared" si="14"/>
         <v>247</v>
@@ -5451,7 +5451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B253" s="10">
         <f t="shared" si="14"/>
         <v>248</v>
@@ -5468,7 +5468,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B254" s="10">
         <f t="shared" si="14"/>
         <v>249</v>
@@ -5485,7 +5485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B255" s="10">
         <f t="shared" ref="B255:B318" si="17">1+B254</f>
         <v>250</v>
@@ -5502,7 +5502,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B256" s="10">
         <f t="shared" si="17"/>
         <v>251</v>
@@ -5519,7 +5519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B257" s="10">
         <f t="shared" si="17"/>
         <v>252</v>
@@ -5536,7 +5536,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B258" s="10">
         <f t="shared" si="17"/>
         <v>253</v>
@@ -5553,7 +5553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B259" s="10">
         <f t="shared" si="17"/>
         <v>254</v>
@@ -5570,7 +5570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B260" s="10">
         <f t="shared" si="17"/>
         <v>255</v>
@@ -5587,7 +5587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B261" s="10">
         <f t="shared" si="17"/>
         <v>256</v>
@@ -5604,7 +5604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B262" s="10">
         <f t="shared" si="17"/>
         <v>257</v>
@@ -5621,7 +5621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B263" s="10">
         <f t="shared" si="17"/>
         <v>258</v>
@@ -5638,7 +5638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B264" s="10">
         <f t="shared" si="17"/>
         <v>259</v>
@@ -5655,7 +5655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B265" s="10">
         <f t="shared" si="17"/>
         <v>260</v>
@@ -5672,7 +5672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B266" s="10">
         <f t="shared" si="17"/>
         <v>261</v>
@@ -5689,7 +5689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B267" s="10">
         <f t="shared" si="17"/>
         <v>262</v>
@@ -5706,7 +5706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B268" s="10">
         <f t="shared" si="17"/>
         <v>263</v>
@@ -5723,7 +5723,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B269" s="10">
         <f t="shared" si="17"/>
         <v>264</v>
@@ -5740,7 +5740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B270" s="10">
         <f t="shared" si="17"/>
         <v>265</v>
@@ -5757,7 +5757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B271" s="10">
         <f t="shared" si="17"/>
         <v>266</v>
@@ -5774,7 +5774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B272" s="10">
         <f t="shared" si="17"/>
         <v>267</v>
@@ -5791,7 +5791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B273" s="10">
         <f t="shared" si="17"/>
         <v>268</v>
@@ -5808,7 +5808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B274" s="10">
         <f t="shared" si="17"/>
         <v>269</v>
@@ -5825,7 +5825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B275" s="10">
         <f t="shared" si="17"/>
         <v>270</v>
@@ -5842,7 +5842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B276" s="10">
         <f t="shared" si="17"/>
         <v>271</v>
@@ -5859,7 +5859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B277" s="10">
         <f t="shared" si="17"/>
         <v>272</v>
@@ -5876,7 +5876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B278" s="10">
         <f t="shared" si="17"/>
         <v>273</v>
@@ -5893,7 +5893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B279" s="10">
         <f t="shared" si="17"/>
         <v>274</v>
@@ -5910,7 +5910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B280" s="10">
         <f t="shared" si="17"/>
         <v>275</v>
@@ -5927,7 +5927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B281" s="10">
         <f t="shared" si="17"/>
         <v>276</v>
@@ -5944,7 +5944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B282" s="10">
         <f t="shared" si="17"/>
         <v>277</v>
@@ -5961,7 +5961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B283" s="10">
         <f t="shared" si="17"/>
         <v>278</v>
@@ -5978,7 +5978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B284" s="10">
         <f t="shared" si="17"/>
         <v>279</v>
@@ -5995,7 +5995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B285" s="10">
         <f t="shared" si="17"/>
         <v>280</v>
@@ -6012,7 +6012,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B286" s="10">
         <f t="shared" si="17"/>
         <v>281</v>
@@ -6029,7 +6029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B287" s="10">
         <f t="shared" si="17"/>
         <v>282</v>
@@ -6046,7 +6046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B288" s="10">
         <f t="shared" si="17"/>
         <v>283</v>
@@ -6063,7 +6063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B289" s="10">
         <f t="shared" si="17"/>
         <v>284</v>
@@ -6080,7 +6080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B290" s="10">
         <f t="shared" si="17"/>
         <v>285</v>
@@ -6097,7 +6097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B291" s="10">
         <f t="shared" si="17"/>
         <v>286</v>
@@ -6114,7 +6114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B292" s="10">
         <f t="shared" si="17"/>
         <v>287</v>
@@ -6131,7 +6131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B293" s="10">
         <f t="shared" si="17"/>
         <v>288</v>
@@ -6148,7 +6148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B294" s="10">
         <f t="shared" si="17"/>
         <v>289</v>
@@ -6165,7 +6165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B295" s="10">
         <f t="shared" si="17"/>
         <v>290</v>
@@ -6182,7 +6182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B296" s="10">
         <f t="shared" si="17"/>
         <v>291</v>
@@ -6199,7 +6199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B297" s="10">
         <f t="shared" si="17"/>
         <v>292</v>
@@ -6216,7 +6216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B298" s="10">
         <f t="shared" si="17"/>
         <v>293</v>
@@ -6233,7 +6233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B299" s="10">
         <f t="shared" si="17"/>
         <v>294</v>
@@ -6250,7 +6250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B300" s="10">
         <f t="shared" si="17"/>
         <v>295</v>
@@ -6267,7 +6267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B301" s="10">
         <f t="shared" si="17"/>
         <v>296</v>
@@ -6284,7 +6284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B302" s="10">
         <f t="shared" si="17"/>
         <v>297</v>
@@ -6301,7 +6301,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B303" s="10">
         <f t="shared" si="17"/>
         <v>298</v>
@@ -6318,7 +6318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B304" s="10">
         <f t="shared" si="17"/>
         <v>299</v>
@@ -6335,7 +6335,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B305" s="10">
         <f t="shared" si="17"/>
         <v>300</v>
@@ -6352,7 +6352,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B306" s="10">
         <f t="shared" si="17"/>
         <v>301</v>
@@ -6369,7 +6369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B307" s="10">
         <f t="shared" si="17"/>
         <v>302</v>
@@ -6386,7 +6386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B308" s="10">
         <f t="shared" si="17"/>
         <v>303</v>
@@ -6403,7 +6403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B309" s="10">
         <f t="shared" si="17"/>
         <v>304</v>
@@ -6420,7 +6420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B310" s="10">
         <f t="shared" si="17"/>
         <v>305</v>
@@ -6437,7 +6437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B311" s="10">
         <f t="shared" si="17"/>
         <v>306</v>
@@ -6454,7 +6454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B312" s="10">
         <f t="shared" si="17"/>
         <v>307</v>
@@ -6471,7 +6471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B313" s="10">
         <f t="shared" si="17"/>
         <v>308</v>
@@ -6488,7 +6488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B314" s="10">
         <f t="shared" si="17"/>
         <v>309</v>
@@ -6505,7 +6505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B315" s="10">
         <f t="shared" si="17"/>
         <v>310</v>
@@ -6522,7 +6522,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B316" s="10">
         <f t="shared" si="17"/>
         <v>311</v>
@@ -6539,7 +6539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B317" s="10">
         <f t="shared" si="17"/>
         <v>312</v>
@@ -6556,7 +6556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B318" s="10">
         <f t="shared" si="17"/>
         <v>313</v>
@@ -6573,7 +6573,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B319" s="10">
         <f t="shared" ref="B319:B340" si="20">1+B318</f>
         <v>314</v>
@@ -6590,7 +6590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B320" s="10">
         <f t="shared" si="20"/>
         <v>315</v>
@@ -6607,7 +6607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B321" s="10">
         <f t="shared" si="20"/>
         <v>316</v>
@@ -6624,7 +6624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B322" s="10">
         <f t="shared" si="20"/>
         <v>317</v>
@@ -6641,7 +6641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B323" s="10">
         <f t="shared" si="20"/>
         <v>318</v>
@@ -6658,7 +6658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B324" s="10">
         <f t="shared" si="20"/>
         <v>319</v>
@@ -6675,7 +6675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B325" s="10">
         <f t="shared" si="20"/>
         <v>320</v>
@@ -6692,7 +6692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B326" s="10">
         <f t="shared" si="20"/>
         <v>321</v>
@@ -6709,7 +6709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B327" s="10">
         <f t="shared" si="20"/>
         <v>322</v>
@@ -6726,7 +6726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B328" s="10">
         <f t="shared" si="20"/>
         <v>323</v>
@@ -6743,7 +6743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B329" s="10">
         <f t="shared" si="20"/>
         <v>324</v>
@@ -6760,7 +6760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B330" s="10">
         <f t="shared" si="20"/>
         <v>325</v>
@@ -6777,7 +6777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B331" s="10">
         <f t="shared" si="20"/>
         <v>326</v>
@@ -6794,7 +6794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B332" s="10">
         <f t="shared" si="20"/>
         <v>327</v>
@@ -6811,7 +6811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B333" s="10">
         <f t="shared" si="20"/>
         <v>328</v>
@@ -6828,7 +6828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B334" s="10">
         <f t="shared" si="20"/>
         <v>329</v>
@@ -6845,7 +6845,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B335" s="10">
         <f t="shared" si="20"/>
         <v>330</v>
@@ -6862,7 +6862,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B336" s="10">
         <f t="shared" si="20"/>
         <v>331</v>
@@ -6879,7 +6879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B337" s="10">
         <f t="shared" si="20"/>
         <v>332</v>
@@ -6896,7 +6896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B338" s="10">
         <f t="shared" si="20"/>
         <v>333</v>
@@ -6913,7 +6913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B339" s="10">
         <f t="shared" si="20"/>
         <v>334</v>
@@ -6930,7 +6930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B340" s="10">
         <f t="shared" si="20"/>
         <v>335</v>
@@ -6960,15 +6960,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE283A69-83AB-4E5A-A62A-C8C4223B902A}">
   <dimension ref="A2:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="92.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="92.5234375" customWidth="1"/>
+    <col min="3" max="3" width="13.15625" customWidth="1"/>
+    <col min="4" max="4" width="15.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="E3" s="17"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -7015,24 +7015,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7043,15 +7043,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692C319B-2B9D-4D5E-8D62-E4C237FCBE25}">
   <dimension ref="A2:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="92.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="92.5234375" customWidth="1"/>
+    <col min="3" max="3" width="13.15625" customWidth="1"/>
+    <col min="4" max="4" width="15.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="E3" s="17"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -7098,24 +7098,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7126,15 +7126,15 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A2:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="100" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.734375" customWidth="1"/>
+    <col min="4" max="4" width="14.5234375" customWidth="1"/>
+    <col min="5" max="5" width="12.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15" t="s">
         <v>4</v>
       </c>
@@ -7164,7 +7164,7 @@
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
         <v>24</v>
       </c>
@@ -7177,14 +7177,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="76.453125" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="76.47265625" customWidth="1"/>
+    <col min="3" max="3" width="12.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15" t="s">
         <v>6</v>
       </c>
@@ -7212,7 +7212,7 @@
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
@@ -7227,15 +7227,15 @@
       </c>
       <c r="E4" s="10"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="9"/>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7245,16 +7245,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:E20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="89.81640625" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="7.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="89.7890625" customWidth="1"/>
+    <col min="3" max="3" width="10.734375" customWidth="1"/>
+    <col min="4" max="4" width="9.15625" customWidth="1"/>
+    <col min="5" max="5" width="7.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7271,7 +7271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="18">
         <v>31</v>
       </c>
@@ -7282,7 +7282,7 @@
       <c r="D3" s="18"/>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10" t="s">
         <v>25</v>
       </c>
@@ -7291,7 +7291,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="18">
         <v>12</v>
       </c>
@@ -7300,7 +7300,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="10">
         <v>11</v>
       </c>
@@ -7309,7 +7309,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="18">
         <v>10</v>
       </c>
@@ -7318,7 +7318,7 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="10">
         <v>9</v>
       </c>
@@ -7327,7 +7327,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="18">
         <v>8</v>
       </c>
@@ -7336,7 +7336,7 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10">
         <v>7</v>
       </c>
@@ -7345,7 +7345,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="18">
         <v>6</v>
       </c>
@@ -7354,7 +7354,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="10">
         <v>5</v>
       </c>
@@ -7363,7 +7363,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="18">
         <v>4</v>
       </c>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="E13" s="18"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="10">
         <v>3</v>
       </c>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="18">
         <v>2</v>
       </c>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="E15" s="18"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="10">
         <v>1</v>
       </c>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="18">
         <v>0</v>
       </c>
@@ -7438,12 +7438,12 @@
       </c>
       <c r="E17" s="18"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="7"/>
     </row>
   </sheetData>
@@ -7455,16 +7455,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:E17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.5234375" customWidth="1"/>
+    <col min="4" max="4" width="13.15625" customWidth="1"/>
+    <col min="5" max="5" width="7.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15">
         <v>31</v>
       </c>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="24" t="s">
         <v>48</v>
       </c>
@@ -7507,7 +7507,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15">
         <v>6</v>
       </c>
@@ -7518,7 +7518,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="24">
         <v>5</v>
       </c>
@@ -7529,7 +7529,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15">
         <v>4</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="24">
         <v>3</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="15">
         <v>2</v>
       </c>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="E9" s="18"/>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="24">
         <v>1</v>
       </c>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="15">
         <v>0</v>
       </c>
@@ -7608,28 +7608,28 @@
       </c>
       <c r="E11" s="18"/>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="25"/>
       <c r="B12" s="4"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="7"/>
     </row>
   </sheetData>
@@ -7641,16 +7641,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB637E7B-A1B0-494F-9CB9-3EBE05669CEA}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="93.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="93.5234375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.7890625" customWidth="1"/>
+    <col min="5" max="5" width="11.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
@@ -7684,12 +7684,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="7"/>
     </row>
   </sheetData>
@@ -7701,16 +7701,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF4887DC-9641-403D-9545-950D8377FEF9}">
   <dimension ref="A2:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="93.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="93.5234375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.7890625" customWidth="1"/>
+    <col min="5" max="5" width="11.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="18" t="s">
         <v>35</v>
       </c>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
@@ -7753,12 +7753,12 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="7"/>
     </row>
   </sheetData>
@@ -7770,16 +7770,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4A4320-DA2C-4E0A-AD8B-18F55EF76D02}">
   <dimension ref="A2:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="93.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="93.5234375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.7890625" customWidth="1"/>
+    <col min="5" max="5" width="11.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15" t="s">
         <v>57</v>
       </c>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="24">
         <v>4</v>
       </c>
@@ -7824,7 +7824,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15">
         <v>3</v>
       </c>
@@ -7837,7 +7837,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="24">
         <v>2</v>
       </c>
@@ -7850,7 +7850,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15">
         <v>1</v>
       </c>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="E7" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="24">
         <v>0</v>
       </c>
@@ -7880,13 +7880,13 @@
       </c>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="25"/>
       <c r="B9" s="4"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
@@ -7900,16 +7900,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6972709-FD1F-472D-BEB9-448A2B1AE61A}">
   <dimension ref="A2:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="93.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="93.5234375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.7890625" customWidth="1"/>
+    <col min="5" max="5" width="11.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15" t="s">
         <v>57</v>
       </c>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="24">
         <v>4</v>
       </c>
@@ -7954,7 +7954,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15">
         <v>3</v>
       </c>
@@ -7967,7 +7967,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -7980,7 +7980,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15">
         <v>2</v>
       </c>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="E7" s="18"/>
     </row>
-    <row r="8" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="24" t="s">
         <v>66</v>
       </c>
@@ -8010,13 +8010,13 @@
       </c>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="25"/>
       <c r="B9" s="4"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="11" t="s">
         <v>7</v>
       </c>
@@ -8030,16 +8030,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65557A7-F759-4E4F-BDE6-7AD601BB2345}">
   <dimension ref="A2:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="89.81640625" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="7.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.15625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="89.7890625" customWidth="1"/>
+    <col min="3" max="3" width="13.3671875" customWidth="1"/>
+    <col min="4" max="4" width="9.15625" customWidth="1"/>
+    <col min="5" max="5" width="7.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="18" t="s">
         <v>92</v>
       </c>
@@ -8069,7 +8069,7 @@
       <c r="D3" s="18"/>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10">
         <v>17</v>
       </c>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="18" t="s">
         <v>91</v>
       </c>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="10">
         <v>8</v>
       </c>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="18" t="s">
         <v>83</v>
       </c>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="E7" s="18"/>
     </row>
-    <row r="8" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="10" t="s">
         <v>82</v>
       </c>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="18" t="s">
         <v>81</v>
       </c>
@@ -8161,12 +8161,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="7" t="s">
         <v>85</v>
       </c>
